--- a/12602984.xlsx
+++ b/12602984.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CAP776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CAP776\Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD241675-11F6-4192-B20C-FCE2E338E5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870AAE38-A3D7-4125-B324-3C6B2897E1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -624,10 +624,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3243,21 +3239,27 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="11"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="12"/>
+      <c r="A52" s="11">
+        <v>46291</v>
+      </c>
+      <c r="B52" s="12">
+        <v>450</v>
+      </c>
+      <c r="C52" s="12">
+        <v>15</v>
+      </c>
       <c r="D52" s="12"/>
       <c r="E52" s="12"/>
       <c r="F52" s="12"/>
       <c r="G52" s="12"/>
       <c r="H52" s="12"/>
-      <c r="I52" s="13" t="str">
+      <c r="I52" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="13" t="str">
+        <v>465</v>
+      </c>
+      <c r="J52" s="13">
         <f t="shared" si="1"/>
-        <v/>
+        <v>975</v>
       </c>
       <c r="K52" s="14"/>
       <c r="L52" s="14"/>

--- a/12602984.xlsx
+++ b/12602984.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CAP776\Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870AAE38-A3D7-4125-B324-3C6B2897E1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC38006-70A3-4730-9E45-26244BFEBF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3248,18 +3248,28 @@
       <c r="C52" s="12">
         <v>15</v>
       </c>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
+      <c r="D52" s="12">
+        <v>150</v>
+      </c>
+      <c r="E52" s="12">
+        <v>20</v>
+      </c>
+      <c r="F52" s="12">
+        <v>60</v>
+      </c>
+      <c r="G52" s="12">
+        <v>1</v>
+      </c>
+      <c r="H52" s="12">
+        <v>30</v>
+      </c>
       <c r="I52" s="13">
         <f t="shared" si="0"/>
-        <v>465</v>
+        <v>725</v>
       </c>
       <c r="J52" s="13">
         <f t="shared" si="1"/>
-        <v>975</v>
+        <v>715</v>
       </c>
       <c r="K52" s="14"/>
       <c r="L52" s="14"/>

--- a/12602984.xlsx
+++ b/12602984.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CAP776\Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC38006-70A3-4730-9E45-26244BFEBF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB743E8-D377-4313-9DA2-FA71E3B76E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3271,8 +3271,12 @@
         <f t="shared" si="1"/>
         <v>715</v>
       </c>
-      <c r="K52" s="14"/>
-      <c r="L52" s="14"/>
+      <c r="K52" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="L52" s="14" t="s">
+        <v>54</v>
+      </c>
       <c r="M52" s="14"/>
       <c r="N52" s="15"/>
     </row>

--- a/12602984.xlsx
+++ b/12602984.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CAP776\Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB743E8-D377-4313-9DA2-FA71E3B76E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F43B19-5E2B-4D91-822E-EE40342B3EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>Busy but managed my work well.</t>
+  </si>
+  <si>
+    <t>A good day with 1 class and free time</t>
   </si>
 </sst>
 </file>
@@ -3238,7 +3241,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="11">
         <v>46291</v>
       </c>
@@ -3277,8 +3280,12 @@
       <c r="L52" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="M52" s="14"/>
-      <c r="N52" s="15"/>
+      <c r="M52" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" s="15" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="11"/>
